--- a/data/trending_integrated_20261016_09.xlsx
+++ b/data/trending_integrated_20261016_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z3"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,60 +563,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1283000</v>
+        <v>19970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+1.66%</t>
+          <t>'+14.31%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>800</v>
+        <v>41</v>
       </c>
       <c r="F2" t="n">
-        <v>515</v>
+        <v>30</v>
       </c>
       <c r="G2" t="n">
-        <v>2117</v>
+        <v>102</v>
       </c>
       <c r="H2" t="n">
-        <v>48.85</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1262000</v>
+        <v>17470</v>
       </c>
       <c r="K2" t="n">
-        <v>1290000</v>
+        <v>18710</v>
       </c>
       <c r="L2" t="n">
-        <v>1298000</v>
+        <v>20200</v>
       </c>
       <c r="M2" t="n">
-        <v>1282000</v>
+        <v>18370</v>
       </c>
       <c r="N2" t="n">
-        <v>49.02</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>361810012500</v>
+        <v>51342732675</v>
       </c>
       <c r="P2" t="n">
-        <v>2987000</v>
+        <v>28800</v>
       </c>
       <c r="Q2" t="n">
-        <v>420500</v>
+        <v>15780</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -626,20 +626,20 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>전일 미국 증시 상승에 힘입어 금일 반등 기대감 형성. 다만, 외국인 수급 확인 전까지는 보수적 접근 필요.</t>
+          <t>반도체 테마 상승에도 불구하고 개인 매도세 및 단일계좌 투주 종목의 급락 가능성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['ADR', '반등', '외국인']</t>
+          <t>['반도체', '개인매도', '급락']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,67 +648,67 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40800</v>
+        <v>14920</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'+1.70%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="F3" t="n">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="G3" t="n">
-        <v>421</v>
+        <v>72</v>
       </c>
       <c r="H3" t="n">
-        <v>12.97</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>40750</v>
+        <v>14670</v>
       </c>
       <c r="K3" t="n">
-        <v>40600</v>
+        <v>14800</v>
       </c>
       <c r="L3" t="n">
-        <v>40800</v>
+        <v>15270</v>
       </c>
       <c r="M3" t="n">
-        <v>40400</v>
+        <v>14800</v>
       </c>
       <c r="N3" t="n">
-        <v>12.84</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>820629400</v>
+        <v>6530069020</v>
       </c>
       <c r="P3" t="n">
-        <v>69200</v>
+        <v>40350</v>
       </c>
       <c r="Q3" t="n">
-        <v>24150</v>
+        <v>3320</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -718,27 +718,395 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>과거 MSCI 퇴출 이후 외국인 비율 변화 주목. 진양곤 회장 관련 언급 존재하나, 뚜렷한 근거 부족.</t>
+          <t>이재명 대통령 관련 정치적 비난과 주가 조작, 뱅크런 의혹 제기. 구체적인 사업 관련 내용은 부실.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>['주가조작', '뱅크런', '정치']</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>64300</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>'+1.58%</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E4" t="n">
+        <v>65</v>
+      </c>
+      <c r="F4" t="n">
+        <v>50</v>
+      </c>
+      <c r="G4" t="n">
+        <v>207</v>
+      </c>
+      <c r="H4" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>63300</v>
+      </c>
+      <c r="K4" t="n">
+        <v>63900</v>
+      </c>
+      <c r="L4" t="n">
+        <v>65500</v>
+      </c>
+      <c r="M4" t="n">
+        <v>63600</v>
+      </c>
+      <c r="N4" t="n">
+        <v>22.11</v>
+      </c>
+      <c r="O4" t="n">
+        <v>24161217650</v>
+      </c>
+      <c r="P4" t="n">
+        <v>139200</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>57000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>뉴스케일파워 상승 마감 언급 및 주가 하락에 대한 불만 표출. 금감원의 미온적 대처 비판.</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
         <v>0.1</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>['MSCI', '외국인', '진양곤']</t>
-        </is>
-      </c>
-      <c r="X3" t="n">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>['뉴스케일파워', '하락', '금감원']</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>212000</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>'+0.95%</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="E5" t="n">
+        <v>800</v>
+      </c>
+      <c r="F5" t="n">
+        <v>531</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1966</v>
+      </c>
+      <c r="H5" t="n">
+        <v>45.98</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>210000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>215000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>215500</v>
+      </c>
+      <c r="M5" t="n">
+        <v>211000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>46.16</v>
+      </c>
+      <c r="O5" t="n">
+        <v>442903153000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>94500</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>반도체 전문 애널리스트의 적정가 제시 및 코스피 야간선물 상승에 따른 단기 급등 전망. 노조 성과급 관련 이슈 언급.</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>['반도체', '적정가', '전망']</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1268000</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>'+0.48%</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="E6" t="n">
+        <v>800</v>
+      </c>
+      <c r="F6" t="n">
+        <v>507</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1571</v>
+      </c>
+      <c r="H6" t="n">
+        <v>48.85</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1262000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1290000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1298000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1264000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>49.02</v>
+      </c>
+      <c r="O6" t="n">
+        <v>843775141000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>420500</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>야간선물 폭등에도 불구하고 주가 반등이 미미하며 급락 가능성 제기. 외인 매도세 관찰.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['반등', '급락', '외인매도']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HLB</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>40400</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>'-0.86%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E7" t="n">
+        <v>86</v>
+      </c>
+      <c r="F7" t="n">
+        <v>62</v>
+      </c>
+      <c r="G7" t="n">
+        <v>433</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>40750</v>
+      </c>
+      <c r="K7" t="n">
+        <v>40600</v>
+      </c>
+      <c r="L7" t="n">
+        <v>41150</v>
+      </c>
+      <c r="M7" t="n">
+        <v>40200</v>
+      </c>
+      <c r="N7" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1936661000</v>
+      </c>
+      <c r="P7" t="n">
+        <v>69200</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>24150</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>담관암 FDA 승인 관련 내용 언급과 외인 매수세 유입 확인. 일부 투자자 불안감 표출.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['FDA승인', '외인매수', '승인']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
         <v>6</v>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>028300</t>
         </is>

--- a/data/trending_integrated_20261016_09.xlsx
+++ b/data/trending_integrated_20261016_09.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19970</v>
+        <v>19180</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+14.31%</t>
+          <t>'+9.79%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G2" t="n">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>18710</v>
       </c>
       <c r="L2" t="n">
-        <v>20200</v>
+        <v>20300</v>
       </c>
       <c r="M2" t="n">
         <v>18370</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>51342732675</v>
+        <v>70874652030</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>반도체 테마 상승에도 불구하고 개인 매도세 및 단일계좌 투주 종목의 급락 가능성 언급.</t>
+          <t>반도체 테마 상승 기대감과 멜콘의 급등 가능성 언급. 단일 계좌 투주 종목.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['반도체', '개인매도', '급락']</t>
+          <t>['반도체 테마', '급등', '단일 계좌']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14920</v>
+        <v>14910</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+1.70%</t>
+          <t>'+1.64%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F3" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G3" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H3" t="n">
         <v>9.779999999999999</v>
@@ -702,7 +702,7 @@
         <v>9.710000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>6530069020</v>
+        <v>8730077605</v>
       </c>
       <c r="P3" t="n">
         <v>40350</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>이재명 대통령 관련 정치적 비난과 주가 조작, 뱅크런 의혹 제기. 구체적인 사업 관련 내용은 부실.</t>
+          <t>주가 조작 및 금감원 사모펀드 긴급 점검, 뱅크런에 대한 우려와 이재명 대통령에 대한 비판.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['주가조작', '뱅크런', '정치']</t>
+          <t>['주가 조작', '뱅크런', '금감원']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>64300</v>
+        <v>212500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.58%</t>
+          <t>'+1.19%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.01</v>
+        <v>-0.18</v>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>50</v>
+        <v>518</v>
       </c>
       <c r="G4" t="n">
-        <v>207</v>
+        <v>1669</v>
       </c>
       <c r="H4" t="n">
-        <v>22.1</v>
+        <v>45.98</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,28 +779,28 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>63300</v>
+        <v>210000</v>
       </c>
       <c r="K4" t="n">
-        <v>63900</v>
+        <v>215000</v>
       </c>
       <c r="L4" t="n">
-        <v>65500</v>
+        <v>215500</v>
       </c>
       <c r="M4" t="n">
-        <v>63600</v>
+        <v>211000</v>
       </c>
       <c r="N4" t="n">
-        <v>22.11</v>
+        <v>46.16</v>
       </c>
       <c r="O4" t="n">
-        <v>24161217650</v>
+        <v>608004749000</v>
       </c>
       <c r="P4" t="n">
-        <v>139200</v>
+        <v>374500</v>
       </c>
       <c r="Q4" t="n">
-        <v>57000</v>
+        <v>94500</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -810,20 +810,20 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>뉴스케일파워 상승 마감 언급 및 주가 하락에 대한 불만 표출. 금감원의 미온적 대처 비판.</t>
+          <t>반도체 전문 애널리스트의 목표가 언급 및 코스피 야간선물 급등에 따른 삼성전자 7% 상승 전망. 노조 성과급 관련 논란.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['뉴스케일파워', '하락', '금감원']</t>
+          <t>['반도체', '목표가', '노조']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>212000</v>
+        <v>63700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.95%</t>
+          <t>'+0.63%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.18</v>
+        <v>-0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>800</v>
+        <v>72</v>
       </c>
       <c r="F5" t="n">
-        <v>531</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>1966</v>
+        <v>226</v>
       </c>
       <c r="H5" t="n">
-        <v>45.98</v>
+        <v>22.1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,28 +871,28 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>210000</v>
+        <v>63300</v>
       </c>
       <c r="K5" t="n">
-        <v>215000</v>
+        <v>63900</v>
       </c>
       <c r="L5" t="n">
-        <v>215500</v>
+        <v>65500</v>
       </c>
       <c r="M5" t="n">
-        <v>211000</v>
+        <v>63600</v>
       </c>
       <c r="N5" t="n">
-        <v>46.16</v>
+        <v>22.11</v>
       </c>
       <c r="O5" t="n">
-        <v>442903153000</v>
+        <v>31988995800</v>
       </c>
       <c r="P5" t="n">
-        <v>374500</v>
+        <v>139200</v>
       </c>
       <c r="Q5" t="n">
-        <v>94500</v>
+        <v>57000</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -902,20 +902,20 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>반도체 전문 애널리스트의 적정가 제시 및 코스피 야간선물 상승에 따른 단기 급등 전망. 노조 성과급 관련 이슈 언급.</t>
+          <t>두산에너빌리티의 단기적 하락 예상과 3분기 매출 하회에 대한 불만. 원전 사업 관련 악재 가능성.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체', '적정가', '전망']</t>
+          <t>['매출 하회', '원전', '하락']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1268000</v>
+        <v>1258000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.48%</t>
+          <t>'-0.32%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>507</v>
+        <v>522</v>
       </c>
       <c r="G6" t="n">
-        <v>1571</v>
+        <v>1411</v>
       </c>
       <c r="H6" t="n">
         <v>48.85</v>
@@ -972,13 +972,13 @@
         <v>1298000</v>
       </c>
       <c r="M6" t="n">
-        <v>1264000</v>
+        <v>1256000</v>
       </c>
       <c r="N6" t="n">
         <v>49.02</v>
       </c>
       <c r="O6" t="n">
-        <v>843775141000</v>
+        <v>1059250588000</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>야간선물 폭등에도 불구하고 주가 반등이 미미하며 급락 가능성 제기. 외인 매도세 관찰.</t>
+          <t>SK하이닉스의 하락세 지속에 대한 부정적 전망과 개인 투자자들의 탈출 시도. 공매도 및 미국 증시 영향.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['반등', '급락', '외인매도']</t>
+          <t>['하락세', '공매도', '탈출']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>40400</v>
+        <v>40350</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.86%</t>
+          <t>'-0.98%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.13</v>
       </c>
       <c r="E7" t="n">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="F7" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="G7" t="n">
-        <v>433</v>
+        <v>482</v>
       </c>
       <c r="H7" t="n">
         <v>12.97</v>
@@ -1064,13 +1064,13 @@
         <v>41150</v>
       </c>
       <c r="M7" t="n">
-        <v>40200</v>
+        <v>40050</v>
       </c>
       <c r="N7" t="n">
         <v>12.84</v>
       </c>
       <c r="O7" t="n">
-        <v>1936661000</v>
+        <v>2915245450</v>
       </c>
       <c r="P7" t="n">
         <v>69200</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>담관암 FDA 승인 관련 내용 언급과 외인 매수세 유입 확인. 일부 투자자 불안감 표출.</t>
+          <t>HLB의 담관암 FDA 승인 관련 기대감과 진양곤 회장의 IR 활동. 외인 매수세 유입.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['FDA승인', '외인매수', '승인']</t>
+          <t>['FDA 승인', 'IR 활동', '외인 매수']</t>
         </is>
       </c>
       <c r="X7" t="n">

--- a/data/trending_integrated_20261016_09.xlsx
+++ b/data/trending_integrated_20261016_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19180</v>
+        <v>8230</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+9.79%</t>
+          <t>'+25.27%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0.26</v>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G2" t="n">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>17470</v>
+        <v>6570</v>
       </c>
       <c r="K2" t="n">
-        <v>18710</v>
+        <v>6850</v>
       </c>
       <c r="L2" t="n">
-        <v>20300</v>
+        <v>8340</v>
       </c>
       <c r="M2" t="n">
-        <v>18370</v>
+        <v>6630</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="O2" t="n">
-        <v>70874652030</v>
+        <v>27155410755</v>
       </c>
       <c r="P2" t="n">
-        <v>28800</v>
+        <v>10300</v>
       </c>
       <c r="Q2" t="n">
-        <v>15780</v>
+        <v>952</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-10000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>반도체 테마 상승 기대감과 멜콘의 급등 가능성 언급. 단일 계좌 투주 종목.</t>
+          <t>군 공항 이전 이슈와 함께 호남 관련주로 분류되어 시장 폭등 가능성이 언급되었습니다. 다만, 투자 경고 종목으로 지정되어 상승에 대한 의문도 제기되었습니다.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['반도체 테마', '급등', '단일 계좌']</t>
+          <t>['군공항이전', '호남관련주', '투자경고']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14910</v>
+        <v>15070</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+1.64%</t>
+          <t>'+2.73%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F3" t="n">
         <v>24</v>
       </c>
       <c r="G3" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H3" t="n">
         <v>9.779999999999999</v>
@@ -702,7 +702,7 @@
         <v>9.710000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>8730077605</v>
+        <v>10821776760</v>
       </c>
       <c r="P3" t="n">
         <v>40350</v>
@@ -711,14 +711,14 @@
         <v>3320</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>주가 조작 및 금감원 사모펀드 긴급 점검, 뱅크런에 대한 우려와 이재명 대통령에 대한 비판.</t>
+          <t>이재명 대통령의 주가 조작 방치 및 금감원의 사모펀드 긴급 점검에 대한 강한 비판과 우려가 반복적으로 제기되었습니다. 뱅크런 가능성과 외인 보유율 관련 언급이 있습니다.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['주가 조작', '뱅크런', '금감원']</t>
+          <t>['주가조작', '뱅크런', '사모펀드']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>212500</v>
+        <v>17880</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.19%</t>
+          <t>'+2.35%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.18</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>800</v>
+        <v>66</v>
       </c>
       <c r="F4" t="n">
-        <v>518</v>
+        <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>1669</v>
+        <v>129</v>
       </c>
       <c r="H4" t="n">
-        <v>45.98</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>210000</v>
+        <v>17470</v>
       </c>
       <c r="K4" t="n">
-        <v>215000</v>
+        <v>18710</v>
       </c>
       <c r="L4" t="n">
-        <v>215500</v>
+        <v>20300</v>
       </c>
       <c r="M4" t="n">
-        <v>211000</v>
+        <v>17630</v>
       </c>
       <c r="N4" t="n">
-        <v>46.16</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>608004749000</v>
+        <v>87477017845</v>
       </c>
       <c r="P4" t="n">
-        <v>374500</v>
+        <v>28800</v>
       </c>
       <c r="Q4" t="n">
-        <v>94500</v>
+        <v>15780</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>반도체 전문 애널리스트의 목표가 언급 및 코스피 야간선물 급등에 따른 삼성전자 7% 상승 전망. 노조 성과급 관련 논란.</t>
+          <t>반도체 테마 내 종목으로 언급되었으나, 단일 계좌 투기 종목으로 분류되어 상승 가능성이 낮다는 의견이 있습니다. 일부 투자자는 고점에서 탈출했다는 언급을 했습니다.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['반도체', '목표가', '노조']</t>
+          <t>['반도체테마', '단일계좌', '투기']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63700</v>
+        <v>64300</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.63%</t>
+          <t>'+1.58%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G5" t="n">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="H5" t="n">
         <v>22.1</v>
@@ -880,13 +880,13 @@
         <v>65500</v>
       </c>
       <c r="M5" t="n">
-        <v>63600</v>
+        <v>63500</v>
       </c>
       <c r="N5" t="n">
         <v>22.11</v>
       </c>
       <c r="O5" t="n">
-        <v>31988995800</v>
+        <v>38915451750</v>
       </c>
       <c r="P5" t="n">
         <v>139200</v>
@@ -895,14 +895,14 @@
         <v>57000</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>두산에너빌리티의 단기적 하락 예상과 3분기 매출 하회에 대한 불만. 원전 사업 관련 악재 가능성.</t>
+          <t>두산에너빌리티의 주가 하락과 3분기 매출 하회에 대한 불만이 제기되었습니다. 송기훈 전문가에 대한 불신과 고의적 하락 의혹, 원전 관련 언급이 있었습니다.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['매출 하회', '원전', '하락']</t>
+          <t>['주가하락', '매출하회', '원전']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1258000</v>
+        <v>212500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.32%</t>
+          <t>'+1.19%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="E6" t="n">
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="G6" t="n">
-        <v>1411</v>
+        <v>1425</v>
       </c>
       <c r="H6" t="n">
-        <v>48.85</v>
+        <v>45.98</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1262000</v>
+        <v>210000</v>
       </c>
       <c r="K6" t="n">
-        <v>1290000</v>
+        <v>215000</v>
       </c>
       <c r="L6" t="n">
-        <v>1298000</v>
+        <v>215500</v>
       </c>
       <c r="M6" t="n">
-        <v>1256000</v>
+        <v>210500</v>
       </c>
       <c r="N6" t="n">
-        <v>49.02</v>
+        <v>46.16</v>
       </c>
       <c r="O6" t="n">
-        <v>1059250588000</v>
+        <v>734417471750</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q6" t="n">
-        <v>420500</v>
+        <v>94500</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-916000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>SK하이닉스의 하락세 지속에 대한 부정적 전망과 개인 투자자들의 탈출 시도. 공매도 및 미국 증시 영향.</t>
+          <t>반도체 전문 애널리스트는 삼성전자 적정가를 7만원으로 제시했으나, 좌파 정권 시 일론머스크와의 거래 기회를 언급하며 부정적인 전망을 내비쳤습니다. 외인 매도 잔여 물량과 노조의 성과급 부결 주장이 언급되었습니다.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['하락세', '공매도', '탈출']</t>
+          <t>['애널리스트', '적정가', '외인매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>40350</v>
+        <v>40850</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.98%</t>
+          <t>'+0.25%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.13</v>
       </c>
       <c r="E7" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="F7" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="G7" t="n">
-        <v>482</v>
+        <v>528</v>
       </c>
       <c r="H7" t="n">
         <v>12.97</v>
@@ -1070,7 +1070,7 @@
         <v>12.84</v>
       </c>
       <c r="O7" t="n">
-        <v>2915245450</v>
+        <v>3602893475</v>
       </c>
       <c r="P7" t="n">
         <v>69200</v>
@@ -1079,14 +1079,14 @@
         <v>24150</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>HLB의 담관암 FDA 승인 관련 기대감과 진양곤 회장의 IR 활동. 외인 매수세 유입.</t>
+          <t>담관암 FDA 승인이라는 긍정적인 뉴스가 있었지만, 일부 투자자는 시장을 이기는 종목은 없다는 점과 상대방(진양곤 회장)의 특성을 언급하며 신중론을 펼치고 있습니다. 외인 매수가 긍정적으로 해석되기도 합니다.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['FDA 승인', 'IR 활동', '외인 매수']</t>
+          <t>['FDA승인', '담관암', '외인매수']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1109,6 +1109,282 @@
       <c r="Z7" t="inlineStr">
         <is>
           <t>028300</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1264000</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>'+0.16%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="E8" t="n">
+        <v>800</v>
+      </c>
+      <c r="F8" t="n">
+        <v>550</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1317</v>
+      </c>
+      <c r="H8" t="n">
+        <v>48.85</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1262000</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1290000</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1298000</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1247000</v>
+      </c>
+      <c r="N8" t="n">
+        <v>49.02</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1339812041000</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>420500</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-146000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>SK하이닉스에 대한 부정적인 전망이 지배적이며, 주가 폭락과 외인 매도, 정부 정책 비판 등이 언급되었습니다. 솔리다임과 최태원 회장 관련 언급도 있었습니다.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['주가폭락', '외인매도', '정부정책']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>진코스텍</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>14450</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>'-3.28%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>48</v>
+      </c>
+      <c r="F9" t="n">
+        <v>31</v>
+      </c>
+      <c r="G9" t="n">
+        <v>70</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>14940</v>
+      </c>
+      <c r="K9" t="n">
+        <v>14940</v>
+      </c>
+      <c r="L9" t="n">
+        <v>16290</v>
+      </c>
+      <c r="M9" t="n">
+        <v>14330</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>18882158685</v>
+      </c>
+      <c r="P9" t="n">
+        <v>30800</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>9810</v>
+      </c>
+      <c r="R9" t="n">
+        <v>9000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>상장 사기 의혹과 함께 주가 급락 가능성이 지속적으로 제기되었습니다. 무능한 경영진에 대한 비판과 함께 시총 하락에 대한 기대감이 언급되었습니다.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['상장사기', '주가급락', '경영진']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>250030</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>라온시큐어</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>19670</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>'-5.20%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>43</v>
+      </c>
+      <c r="F10" t="n">
+        <v>34</v>
+      </c>
+      <c r="G10" t="n">
+        <v>123</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>20750</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20500</v>
+      </c>
+      <c r="L10" t="n">
+        <v>21500</v>
+      </c>
+      <c r="M10" t="n">
+        <v>19440</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O10" t="n">
+        <v>23368726925</v>
+      </c>
+      <c r="P10" t="n">
+        <v>22450</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>6320</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>보안 관련 해킹 사고 증가와 함께 신규 납품 요청 및 러브콜이 쇄도한다는 긍정적 뉴스가 있었으나, 주가 급락 및 하한가 가능성 언급 등 부정적 전망도 혼재합니다.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>['보안', '해킹', '납품']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>042510</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261016_09.xlsx
+++ b/data/trending_integrated_20261016_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:Z11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8230</v>
+        <v>8410</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+25.27%</t>
+          <t>'+28.01%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.26</v>
       </c>
       <c r="E2" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G2" t="n">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="H2" t="n">
         <v>0.73</v>
@@ -601,7 +601,7 @@
         <v>6850</v>
       </c>
       <c r="L2" t="n">
-        <v>8340</v>
+        <v>8540</v>
       </c>
       <c r="M2" t="n">
         <v>6630</v>
@@ -610,7 +610,7 @@
         <v>0.99</v>
       </c>
       <c r="O2" t="n">
-        <v>27155410755</v>
+        <v>39404055245</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>군 공항 이전 이슈와 함께 호남 관련주로 분류되어 시장 폭등 가능성이 언급되었습니다. 다만, 투자 경고 종목으로 지정되어 상승에 대한 의문도 제기되었습니다.</t>
+          <t>군공항 이전 관련 호재와 함께 매물대 돌파 시 상한가 가능성 언급, 테마주 흐름에 따른 매수 및 매도 타이밍 제시.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['군공항이전', '호남관련주', '투자경고']</t>
+          <t>['군공항이전', '테마대장', '매물대']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,83 +655,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15070</v>
+        <v>8160</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+2.73%</t>
+          <t>'+14.13%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.07000000000000001</v>
+        <v>-1.12</v>
       </c>
       <c r="E3" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="F3" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G3" t="n">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="H3" t="n">
-        <v>9.779999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>14670</v>
+        <v>7150</v>
       </c>
       <c r="K3" t="n">
-        <v>14800</v>
+        <v>7430</v>
       </c>
       <c r="L3" t="n">
-        <v>15270</v>
+        <v>8600</v>
       </c>
       <c r="M3" t="n">
-        <v>14800</v>
+        <v>7300</v>
       </c>
       <c r="N3" t="n">
-        <v>9.710000000000001</v>
+        <v>1.84</v>
       </c>
       <c r="O3" t="n">
-        <v>10821776760</v>
+        <v>75118635130</v>
       </c>
       <c r="P3" t="n">
-        <v>40350</v>
+        <v>8600</v>
       </c>
       <c r="Q3" t="n">
-        <v>3320</v>
+        <v>2270</v>
       </c>
       <c r="R3" t="n">
-        <v>-7000</v>
+        <v>93000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>이재명 대통령의 주가 조작 방치 및 금감원의 사모펀드 긴급 점검에 대한 강한 비판과 우려가 반복적으로 제기되었습니다. 뱅크런 가능성과 외인 보유율 관련 언급이 있습니다.</t>
+          <t>재료 부각에 따른 신고가 및 텐버거 가능성 언급하며 긍정적 전망 제시, 매수 기회 포착 시도.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['주가조작', '뱅크런', '사모펀드']</t>
+          <t>['텐버거', '신고가', '재료']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17880</v>
+        <v>18000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.35%</t>
+          <t>'+3.03%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F4" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>87477017845</v>
+        <v>96898663825</v>
       </c>
       <c r="P4" t="n">
         <v>28800</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>반도체 테마 내 종목으로 언급되었으나, 단일 계좌 투기 종목으로 분류되어 상승 가능성이 낮다는 의견이 있습니다. 일부 투자자는 고점에서 탈출했다는 언급을 했습니다.</t>
+          <t>반도체 테마 및 단일 계좌 이슈로 인한 하락 가능성 경고, 과거 매도 성공 경험을 바탕으로 추가 하락 및 탈출을 권고.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['반도체테마', '단일계좌', '투기']</t>
+          <t>['단일계좌', '반도체테마', '음봉패턴']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64300</v>
+        <v>15090</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.58%</t>
+          <t>'+2.86%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="F5" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="G5" t="n">
-        <v>245</v>
+        <v>83</v>
       </c>
       <c r="H5" t="n">
-        <v>22.1</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>63300</v>
+        <v>14670</v>
       </c>
       <c r="K5" t="n">
-        <v>63900</v>
+        <v>14800</v>
       </c>
       <c r="L5" t="n">
-        <v>65500</v>
+        <v>15270</v>
       </c>
       <c r="M5" t="n">
-        <v>63500</v>
+        <v>14800</v>
       </c>
       <c r="N5" t="n">
-        <v>22.11</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>38915451750</v>
+        <v>11843110110</v>
       </c>
       <c r="P5" t="n">
-        <v>139200</v>
+        <v>40350</v>
       </c>
       <c r="Q5" t="n">
-        <v>57000</v>
+        <v>3320</v>
       </c>
       <c r="R5" t="n">
-        <v>22000</v>
+        <v>-7000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>두산에너빌리티의 주가 하락과 3분기 매출 하회에 대한 불만이 제기되었습니다. 송기훈 전문가에 대한 불신과 고의적 하락 의혹, 원전 관련 언급이 있었습니다.</t>
+          <t>정치인의 주가 조작 관련 의혹 제기와 함께 금융 감독원의 긴급 점검 및 뱅크런 가능성에 대한 우려를 반복적으로 제기.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['주가하락', '매출하회', '원전']</t>
+          <t>['주가조작', '사모펀드', '뱅크런']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>212500</v>
+        <v>64400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.19%</t>
+          <t>'+1.74%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.18</v>
+        <v>-0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>84</v>
       </c>
       <c r="F6" t="n">
-        <v>519</v>
+        <v>55</v>
       </c>
       <c r="G6" t="n">
-        <v>1425</v>
+        <v>289</v>
       </c>
       <c r="H6" t="n">
-        <v>45.98</v>
+        <v>22.1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>210000</v>
+        <v>63300</v>
       </c>
       <c r="K6" t="n">
-        <v>215000</v>
+        <v>63900</v>
       </c>
       <c r="L6" t="n">
-        <v>215500</v>
+        <v>65500</v>
       </c>
       <c r="M6" t="n">
-        <v>210500</v>
+        <v>63500</v>
       </c>
       <c r="N6" t="n">
-        <v>46.16</v>
+        <v>22.11</v>
       </c>
       <c r="O6" t="n">
-        <v>734417471750</v>
+        <v>43310322550</v>
       </c>
       <c r="P6" t="n">
-        <v>374500</v>
+        <v>139200</v>
       </c>
       <c r="Q6" t="n">
-        <v>94500</v>
+        <v>57000</v>
       </c>
       <c r="R6" t="n">
-        <v>-916000</v>
+        <v>22000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>반도체 전문 애널리스트는 삼성전자 적정가를 7만원으로 제시했으나, 좌파 정권 시 일론머스크와의 거래 기회를 언급하며 부정적인 전망을 내비쳤습니다. 외인 매도 잔여 물량과 노조의 성과급 부결 주장이 언급되었습니다.</t>
+          <t>뉴스케일파워 상승 대비 부진한 흐름에 대한 불만과 함께, 고가 매수 후 하락 및 금감원 미개입에 대한 비판 제기.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['애널리스트', '적정가', '외인매도']</t>
+          <t>['뉴스케일파워', '매물대', '금감원']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>40850</v>
+        <v>213500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.25%</t>
+          <t>'+1.67%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.13</v>
+        <v>-0.18</v>
       </c>
       <c r="E7" t="n">
-        <v>119</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>83</v>
+        <v>517</v>
       </c>
       <c r="G7" t="n">
-        <v>528</v>
+        <v>1362</v>
       </c>
       <c r="H7" t="n">
-        <v>12.97</v>
+        <v>45.98</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>40750</v>
+        <v>210000</v>
       </c>
       <c r="K7" t="n">
-        <v>40600</v>
+        <v>215000</v>
       </c>
       <c r="L7" t="n">
-        <v>41150</v>
+        <v>215500</v>
       </c>
       <c r="M7" t="n">
-        <v>40050</v>
+        <v>210500</v>
       </c>
       <c r="N7" t="n">
-        <v>12.84</v>
+        <v>46.16</v>
       </c>
       <c r="O7" t="n">
-        <v>3602893475</v>
+        <v>811096324000</v>
       </c>
       <c r="P7" t="n">
-        <v>69200</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>24150</v>
+        <v>94500</v>
       </c>
       <c r="R7" t="n">
-        <v>-3000</v>
+        <v>-916000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>담관암 FDA 승인이라는 긍정적인 뉴스가 있었지만, 일부 투자자는 시장을 이기는 종목은 없다는 점과 상대방(진양곤 회장)의 특성을 언급하며 신중론을 펼치고 있습니다. 외인 매수가 긍정적으로 해석되기도 합니다.</t>
+          <t>정권 교체 및 노조 관련 부정적 전망과 함께 외인 매도, 프로그램 매도에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['FDA승인', '담관암', '외인매수']</t>
+          <t>['외인매도', '노조', '프로그램매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1264000</v>
+        <v>41250</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.16%</t>
+          <t>'+1.23%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.17</v>
+        <v>0.13</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>129</v>
       </c>
       <c r="F8" t="n">
-        <v>550</v>
+        <v>86</v>
       </c>
       <c r="G8" t="n">
-        <v>1317</v>
+        <v>545</v>
       </c>
       <c r="H8" t="n">
-        <v>48.85</v>
+        <v>12.97</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1262000</v>
+        <v>40750</v>
       </c>
       <c r="K8" t="n">
-        <v>1290000</v>
+        <v>40600</v>
       </c>
       <c r="L8" t="n">
-        <v>1298000</v>
+        <v>41350</v>
       </c>
       <c r="M8" t="n">
-        <v>1247000</v>
+        <v>40050</v>
       </c>
       <c r="N8" t="n">
-        <v>49.02</v>
+        <v>12.84</v>
       </c>
       <c r="O8" t="n">
-        <v>1339812041000</v>
+        <v>4545385925</v>
       </c>
       <c r="P8" t="n">
-        <v>2987000</v>
+        <v>69200</v>
       </c>
       <c r="Q8" t="n">
-        <v>420500</v>
+        <v>24150</v>
       </c>
       <c r="R8" t="n">
-        <v>-146000</v>
+        <v>-3000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>SK하이닉스에 대한 부정적인 전망이 지배적이며, 주가 폭락과 외인 매도, 정부 정책 비판 등이 언급되었습니다. 솔리다임과 최태원 회장 관련 언급도 있었습니다.</t>
+          <t>담관암 FDA 승인이라는 긍정적인 뉴스가 있었지만, 일부 투자자는 시장을 이기는 종목은 없다는 점과 상대방(진양곤 회장)의 특성을 언급하며 신중론을 펼치고 있습니다. 외인 매수가 긍정적으로 해석되기도 합니다.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['주가폭락', '외인매도', '정부정책']</t>
+          <t>['FDA승인', '담관암', '외인매수']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14450</v>
+        <v>1273000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.28%</t>
+          <t>'+0.87%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="E9" t="n">
-        <v>48</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>31</v>
+        <v>565</v>
       </c>
       <c r="G9" t="n">
-        <v>70</v>
+        <v>1393</v>
       </c>
       <c r="H9" t="n">
-        <v>0.11</v>
+        <v>48.85</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14940</v>
+        <v>1262000</v>
       </c>
       <c r="K9" t="n">
-        <v>14940</v>
+        <v>1290000</v>
       </c>
       <c r="L9" t="n">
-        <v>16290</v>
+        <v>1298000</v>
       </c>
       <c r="M9" t="n">
-        <v>14330</v>
+        <v>1247000</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>49.02</v>
       </c>
       <c r="O9" t="n">
-        <v>18882158685</v>
+        <v>1485199522500</v>
       </c>
       <c r="P9" t="n">
-        <v>30800</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>9810</v>
+        <v>420500</v>
       </c>
       <c r="R9" t="n">
-        <v>9000</v>
+        <v>-146000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>상장 사기 의혹과 함께 주가 급락 가능성이 지속적으로 제기되었습니다. 무능한 경영진에 대한 비판과 함께 시총 하락에 대한 기대감이 언급되었습니다.</t>
+          <t>정치적 이슈와 연관 지어 부정적 전망을 제시하며, 주가 하락 및 오너 리스크에 대한 우려를 표출.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['상장사기', '주가급락', '경영진']</t>
+          <t>['정치이슈', '오너리스크', '주가하락']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>250030</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19670</v>
+        <v>14520</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-5.20%</t>
+          <t>'-2.81%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="F10" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="H10" t="n">
-        <v>4.28</v>
+        <v>0.11</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,38 +1331,38 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>20750</v>
+        <v>14940</v>
       </c>
       <c r="K10" t="n">
-        <v>20500</v>
+        <v>14940</v>
       </c>
       <c r="L10" t="n">
-        <v>21500</v>
+        <v>16290</v>
       </c>
       <c r="M10" t="n">
-        <v>19440</v>
+        <v>14330</v>
       </c>
       <c r="N10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>23368726925</v>
+        <v>19808821860</v>
       </c>
       <c r="P10" t="n">
-        <v>22450</v>
+        <v>30800</v>
       </c>
       <c r="Q10" t="n">
-        <v>6320</v>
+        <v>9810</v>
       </c>
       <c r="R10" t="n">
-        <v>3000</v>
+        <v>9000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>보안 관련 해킹 사고 증가와 함께 신규 납품 요청 및 러브콜이 쇄도한다는 긍정적 뉴스가 있었으나, 주가 급락 및 하한가 가능성 언급 등 부정적 전망도 혼재합니다.</t>
+          <t>상장 사기 의혹 제기하며 주가 조작 및 시총 급락 가능성 언급, 투자자 이탈 및 법적 심판 경고.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,18 +1371,110 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['보안', '해킹', '납품']</t>
+          <t>['상장사기', '주가조작', '시총']</t>
         </is>
       </c>
       <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>250030</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>라온시큐어</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20100</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>'-3.13%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>49</v>
+      </c>
+      <c r="F11" t="n">
+        <v>35</v>
+      </c>
+      <c r="G11" t="n">
+        <v>130</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>20750</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20500</v>
+      </c>
+      <c r="L11" t="n">
+        <v>21500</v>
+      </c>
+      <c r="M11" t="n">
+        <v>19440</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O11" t="n">
+        <v>24814799955</v>
+      </c>
+      <c r="P11" t="n">
+        <v>22450</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>6320</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>해킹 사고 증가와 연관 지어 보안주로서의 부각 가능성 언급, 신규 납품 요청 및 긍정적 수급 상황을 근거로 상승 기대.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['보안주', '해킹사고', '신규납품']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
         <v>2</v>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>042510</t>
         </is>

--- a/data/trending_integrated_20261016_09.xlsx
+++ b/data/trending_integrated_20261016_09.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8410</v>
+        <v>8070</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+28.01%</t>
+          <t>'+22.83%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.26</v>
       </c>
       <c r="E2" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="F2" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="H2" t="n">
         <v>0.73</v>
@@ -610,7 +610,7 @@
         <v>0.99</v>
       </c>
       <c r="O2" t="n">
-        <v>39404055245</v>
+        <v>45340611095</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>군공항 이전 관련 호재와 함께 매물대 돌파 시 상한가 가능성 언급, 테마주 흐름에 따른 매수 및 매도 타이밍 제시.</t>
+          <t>군공항 이전 관련 이슈 언급. 8만원 가능성 및 상한가 기대. 외인 수급 상승 및 투자경고 종목.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['군공항이전', '테마대장', '매물대']</t>
+          <t>['군공항', '상한가', '투자경고']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8160</v>
+        <v>8200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.13%</t>
+          <t>'+14.69%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-1.12</v>
       </c>
       <c r="E3" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F3" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G3" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H3" t="n">
         <v>0.72</v>
@@ -702,7 +702,7 @@
         <v>1.84</v>
       </c>
       <c r="O3" t="n">
-        <v>75118635130</v>
+        <v>83403113305</v>
       </c>
       <c r="P3" t="n">
         <v>8600</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>재료 부각에 따른 신고가 및 텐버거 가능성 언급하며 긍정적 전망 제시, 매수 기회 포착 시도.</t>
+          <t>뉴로메가 사례를 들며 텐버거 가능성 언급. 10만원 목표 및 신고가 기대. 외인 매도세 속 종목 저점 매수 고려.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['텐버거', '신고가', '재료']</t>
+          <t>['텐버거', '신고가', '저점매수']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18000</v>
+        <v>18350</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+3.03%</t>
+          <t>'+5.04%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>96898663825</v>
+        <v>103631507975</v>
       </c>
       <c r="P4" t="n">
         <v>28800</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>반도체 테마 및 단일 계좌 이슈로 인한 하락 가능성 경고, 과거 매도 성공 경험을 바탕으로 추가 하락 및 탈출을 권고.</t>
+          <t>반도체 테마 관련 언급과 함께 단일 계좌 투매 및 급락 가능성 경고. 일본 및 호남 반도체 공장 수혜주 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['단일계좌', '반도체테마', '음봉패턴']</t>
+          <t>['반도체', '투매', '급락']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15090</v>
+        <v>15095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+2.86%</t>
+          <t>'+2.90%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G5" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H5" t="n">
         <v>9.779999999999999</v>
@@ -886,7 +886,7 @@
         <v>9.710000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>11843110110</v>
+        <v>12470162740</v>
       </c>
       <c r="P5" t="n">
         <v>40350</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치인의 주가 조작 관련 의혹 제기와 함께 금융 감독원의 긴급 점검 및 뱅크런 가능성에 대한 우려를 반복적으로 제기.</t>
+          <t>정치인 및 금융당국에 대한 비판과 함께 주가 조작, 뱅크런, 사모펀드 점검 등 불확실한 내용 언급. 200일선 회복 중요성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['주가조작', '사모펀드', '뱅크런']</t>
+          <t>['주가조작', '뱅크런', '사모펀드']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>64400</v>
+        <v>65000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.74%</t>
+          <t>'+2.69%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F6" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G6" t="n">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="H6" t="n">
         <v>22.1</v>
@@ -978,7 +978,7 @@
         <v>22.11</v>
       </c>
       <c r="O6" t="n">
-        <v>43310322550</v>
+        <v>49707000950</v>
       </c>
       <c r="P6" t="n">
         <v>139200</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>뉴스케일파워 상승 대비 부진한 흐름에 대한 불만과 함께, 고가 매수 후 하락 및 금감원 미개입에 대한 비판 제기.</t>
+          <t>뉴스케일파워 상승 언급과 함께 3분기 매출 하회 및 63300원 하락 시 55000원까지 추가 하락 가능성 언급. 금감원 비판.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['뉴스케일파워', '매물대', '금감원']</t>
+          <t>['매출하회', '추가하락', '금감원']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>213500</v>
+        <v>215000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.67%</t>
+          <t>'+2.38%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="G7" t="n">
-        <v>1362</v>
+        <v>1345</v>
       </c>
       <c r="H7" t="n">
         <v>45.98</v>
@@ -1070,7 +1070,7 @@
         <v>46.16</v>
       </c>
       <c r="O7" t="n">
-        <v>811096324000</v>
+        <v>911018484500</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정권 교체 및 노조 관련 부정적 전망과 함께 외인 매도, 프로그램 매도에 대한 우려 제기.</t>
+          <t>정치적 이슈 언급과 함께 개인 투자자들의 매도 및 폭락 기원 언급. 외인 매도 물량에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['외인매도', '노조', '프로그램매도']</t>
+          <t>['이재명', '노조', '외인매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,83 +1115,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>41250</v>
+        <v>1290000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+1.23%</t>
+          <t>'+2.22%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.13</v>
+        <v>-0.17</v>
       </c>
       <c r="E8" t="n">
-        <v>129</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>86</v>
+        <v>553</v>
       </c>
       <c r="G8" t="n">
-        <v>545</v>
+        <v>1340</v>
       </c>
       <c r="H8" t="n">
-        <v>12.97</v>
+        <v>48.85</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>40750</v>
+        <v>1262000</v>
       </c>
       <c r="K8" t="n">
-        <v>40600</v>
+        <v>1290000</v>
       </c>
       <c r="L8" t="n">
-        <v>41350</v>
+        <v>1298000</v>
       </c>
       <c r="M8" t="n">
-        <v>40050</v>
+        <v>1247000</v>
       </c>
       <c r="N8" t="n">
-        <v>12.84</v>
+        <v>49.02</v>
       </c>
       <c r="O8" t="n">
-        <v>4545385925</v>
+        <v>1727257954500</v>
       </c>
       <c r="P8" t="n">
-        <v>69200</v>
+        <v>2987000</v>
       </c>
       <c r="Q8" t="n">
-        <v>24150</v>
+        <v>420500</v>
       </c>
       <c r="R8" t="n">
-        <v>-3000</v>
+        <v>-146000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>담관암 FDA 승인이라는 긍정적인 뉴스가 있었지만, 일부 투자자는 시장을 이기는 종목은 없다는 점과 상대방(진양곤 회장)의 특성을 언급하며 신중론을 펼치고 있습니다. 외인 매수가 긍정적으로 해석되기도 합니다.</t>
+          <t>정치적 인물 및 정부 정책 비판과 함께 종목의 급락 예상 및 오너 리스크 언급. 솔리다임 관련 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['FDA승인', '담관암', '외인매수']</t>
+          <t>['이재명', '오너리스크', '솔리다임']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1273000</v>
+        <v>41050</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.87%</t>
+          <t>'+0.74%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.17</v>
+        <v>0.13</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>141</v>
       </c>
       <c r="F9" t="n">
-        <v>565</v>
+        <v>94</v>
       </c>
       <c r="G9" t="n">
-        <v>1393</v>
+        <v>579</v>
       </c>
       <c r="H9" t="n">
-        <v>48.85</v>
+        <v>12.97</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1262000</v>
+        <v>40750</v>
       </c>
       <c r="K9" t="n">
-        <v>1290000</v>
+        <v>40600</v>
       </c>
       <c r="L9" t="n">
-        <v>1298000</v>
+        <v>41450</v>
       </c>
       <c r="M9" t="n">
-        <v>1247000</v>
+        <v>40050</v>
       </c>
       <c r="N9" t="n">
-        <v>49.02</v>
+        <v>12.84</v>
       </c>
       <c r="O9" t="n">
-        <v>1485199522500</v>
+        <v>5245662150</v>
       </c>
       <c r="P9" t="n">
-        <v>2987000</v>
+        <v>69200</v>
       </c>
       <c r="Q9" t="n">
-        <v>420500</v>
+        <v>24150</v>
       </c>
       <c r="R9" t="n">
-        <v>-146000</v>
+        <v>-3000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연관 지어 부정적 전망을 제시하며, 주가 하락 및 오너 리스크에 대한 우려를 표출.</t>
+          <t>담관암 FDA 승인 기대감과 함께 야간 선물 상승 및 외인 매수세 언급. 환희에 팔라는 경고도 존재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['정치이슈', '오너리스크', '주가하락']</t>
+          <t>['FDA승인', '야간선물', '외인매수']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14520</v>
+        <v>14550</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.81%</t>
+          <t>'-2.61%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G10" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="H10" t="n">
         <v>0.11</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>19808821860</v>
+        <v>20520241900</v>
       </c>
       <c r="P10" t="n">
         <v>30800</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>상장 사기 의혹 제기하며 주가 조작 및 시총 급락 가능성 언급, 투자자 이탈 및 법적 심판 경고.</t>
+          <t>상장 사기 의혹 및 코넥스 주가 띄우기 후 매도 가능성 제기. 시총 급락 및 법적 심판 언급. 신규주 패턴 지적.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['상장사기', '주가조작', '시총']</t>
+          <t>['상장사기', '코넥스', '신규주']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1406,13 +1406,13 @@
         <v>2.5</v>
       </c>
       <c r="E11" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F11" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G11" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="H11" t="n">
         <v>4.28</v>
@@ -1438,7 +1438,7 @@
         <v>1.78</v>
       </c>
       <c r="O11" t="n">
-        <v>24814799955</v>
+        <v>27135448620</v>
       </c>
       <c r="P11" t="n">
         <v>22450</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>해킹 사고 증가와 연관 지어 보안주로서의 부각 가능성 언급, 신규 납품 요청 및 긍정적 수급 상황을 근거로 상승 기대.</t>
+          <t>해킹 시도 증가 관련 뉴스와 함께 농협, KDB 방어 성공 및 신규 납품 요청, 러브콜 쇄도 언급. 연기금 매수 추정.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['보안주', '해킹사고', '신규납품']</t>
+          <t>['해킹', '보안', '납품']</t>
         </is>
       </c>
       <c r="X11" t="n">
